--- a/artfynd/A 25610-2026 artfynd.xlsx
+++ b/artfynd/A 25610-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132769825</v>
+        <v>132776086</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Höjdaåsen, Höjdaåsen, Vstm</t>
+          <t>Kringlan, Kringlan, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486549</v>
+        <v>486580</v>
       </c>
       <c r="R2" t="n">
-        <v>6615069</v>
+        <v>6614942</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +785,7 @@
         <v>132773865</v>
       </c>
       <c r="B3" t="n">
-        <v>93244</v>
+        <v>93309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132771869</v>
+        <v>132769917</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -925,22 +920,22 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gladtjärnen, Gladtjärnen, Vstm</t>
+          <t>Höjdaåsen, Höjdaåsen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486354</v>
+        <v>486559</v>
       </c>
       <c r="R4" t="n">
-        <v>6615113</v>
+        <v>6615026</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,19 +962,9 @@
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132776255</v>
+        <v>132769982</v>
       </c>
       <c r="B5" t="n">
-        <v>4775</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,34 +1002,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kringlan, Kringlan, Vstm</t>
+          <t>Gladtjärnen, Gladtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486575</v>
+        <v>486523</v>
       </c>
       <c r="R5" t="n">
-        <v>6614881</v>
+        <v>6615068</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132773599</v>
+        <v>132770184</v>
       </c>
       <c r="B6" t="n">
-        <v>8455</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,37 +1114,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gladtjärnen, Gladtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486298</v>
+        <v>486479</v>
       </c>
       <c r="R6" t="n">
-        <v>6614965</v>
+        <v>6615101</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,19 +1179,9 @@
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,60 +1196,68 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132776086</v>
+        <v>132867113</v>
       </c>
       <c r="B7" t="n">
-        <v>91918</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kringlan, Kringlan, Vstm</t>
+          <t>Lönnvaldstorp, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486580</v>
+        <v>486182</v>
       </c>
       <c r="R7" t="n">
-        <v>6614942</v>
+        <v>6615134</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,19 +1284,9 @@
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,22 +1301,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Maria Engblom</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Maria Engblom</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132769982</v>
+        <v>132769825</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,16 +1324,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1358,19 +1344,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gladtjärnen, Gladtjärnen, Vstm</t>
+          <t>Höjdaåsen, Höjdaåsen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486523</v>
+        <v>486549</v>
       </c>
       <c r="R8" t="n">
-        <v>6615068</v>
+        <v>6615069</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1402,7 +1388,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1398,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,45 +1425,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132776412</v>
+        <v>132771869</v>
       </c>
       <c r="B9" t="n">
-        <v>4775</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Höjdaåsen, Höjdaåsen, Vstm</t>
+          <t>Gladtjärnen, Gladtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486616</v>
+        <v>486354</v>
       </c>
       <c r="R9" t="n">
-        <v>6615024</v>
+        <v>6615113</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1509,7 +1500,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1510,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132770448</v>
+        <v>132769436</v>
       </c>
       <c r="B10" t="n">
-        <v>5179</v>
+        <v>57162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1548,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gladtjärnen, Gladtjärnen, Vstm</t>
+          <t>Höjdaåsen, Höjdaåsen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486460</v>
+        <v>486746</v>
       </c>
       <c r="R10" t="n">
-        <v>6615111</v>
+        <v>6615020</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1616,7 +1612,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1622,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,32 +1649,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132770184</v>
+        <v>132867437</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>57162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,23 +1682,23 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gladtjärnen, Gladtjärnen, Vstm</t>
+          <t>Lönnvaldstorp, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486479</v>
+        <v>486168</v>
       </c>
       <c r="R11" t="n">
-        <v>6615101</v>
+        <v>6614759</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,22 +1742,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Maria Engblom</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Maria Engblom</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132776250</v>
+        <v>132776255</v>
       </c>
       <c r="B12" t="n">
-        <v>5179</v>
+        <v>4776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,46 +1765,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Höjdaåsen, Höjdaåsen, Vstm</t>
+          <t>Kringlan, Kringlan, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486614</v>
+        <v>486575</v>
       </c>
       <c r="R12" t="n">
-        <v>6614995</v>
+        <v>6614881</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1835,83 +1822,87 @@
           <t>2026-04-25</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132769917</v>
+        <v>132776412</v>
       </c>
       <c r="B13" t="n">
-        <v>57955</v>
+        <v>4776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Höjdaåsen, Höjdaåsen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486559</v>
+        <v>486616</v>
       </c>
       <c r="R13" t="n">
-        <v>6615026</v>
+        <v>6615024</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1938,9 +1929,19 @@
           <t>2026-04-25</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,68 +1956,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132867113</v>
+        <v>132770448</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>5181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lönnvaldstorp, Vstm</t>
+          <t>Gladtjärnen, Gladtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486182</v>
+        <v>486460</v>
       </c>
       <c r="R14" t="n">
-        <v>6615134</v>
+        <v>6615111</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2043,9 +2036,19 @@
           <t>2026-04-25</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,22 +2063,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Engblom</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Engblom</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132867437</v>
+        <v>132776250</v>
       </c>
       <c r="B15" t="n">
-        <v>57145</v>
+        <v>5181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,45 +2086,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lönnvaldstorp, Vstm</t>
+          <t>Höjdaåsen, Höjdaåsen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486168</v>
+        <v>486614</v>
       </c>
       <c r="R15" t="n">
-        <v>6614759</v>
+        <v>6614995</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2159,28 +2163,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Engblom</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Engblom</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132866529</v>
+        <v>132773599</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,24 +2211,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lönnvaldstorp, Vstm</t>
+          <t>Gladtjärnen, Gladtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486436</v>
+        <v>486298</v>
       </c>
       <c r="R16" t="n">
-        <v>6615075</v>
+        <v>6614965</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2250,33 +2250,145 @@
           <t>2026-04-25</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132866529</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lönnvaldstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>486436</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6615075</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Järnboås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Maria Engblom</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Maria Engblom</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25610-2026 artfynd.xlsx
+++ b/artfynd/A 25610-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132776086</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135019600</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132773865</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132769917</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132769982</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132770184</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132867113</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,6 +1569,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134694109</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132769825</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1753,6 +1803,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132771869</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1865,6 +1920,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134695205</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1977,6 +2037,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132769436</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2082,6 +2147,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132867437</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2189,6 +2259,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132776255</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2296,6 +2371,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132776412</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2403,6 +2483,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134694942</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2510,6 +2595,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135019474</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2617,6 +2707,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132770448</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2724,6 +2819,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132776250</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2831,6 +2931,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132773599</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2934,8 +3039,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132866529</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25610-2026 artfynd.xlsx
+++ b/artfynd/A 25610-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135019600</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25610-2026 artfynd.xlsx
+++ b/artfynd/A 25610-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135019600</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
